--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -1,196 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134A6EE6-5719-4838-9DDD-BDEA4E42ED29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
-  <si>
-    <t>Num</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Pasos</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Obtained Result</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Menus' home</t>
-  </si>
-  <si>
-    <t>MEN001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user sees the menus' home
-</t>
-  </si>
-  <si>
-    <t>1. The menus' home is correctly.</t>
-  </si>
-  <si>
-    <t>1. The menus' home is not correctly.</t>
-  </si>
-  <si>
-    <t>MEN002</t>
-  </si>
-  <si>
-    <t>Create menu</t>
-  </si>
-  <si>
-    <t>Modify menu</t>
-  </si>
-  <si>
-    <t>Delete menu</t>
-  </si>
-  <si>
-    <t>MEN003</t>
-  </si>
-  <si>
-    <t>MEN004</t>
-  </si>
-  <si>
-    <t>MEN005</t>
-  </si>
-  <si>
-    <t>Required fields are missing</t>
-  </si>
-  <si>
-    <t>1. An error is shown</t>
-  </si>
-  <si>
-    <t>1. The menu is created.</t>
-  </si>
-  <si>
-    <t>1. The menu is modified.</t>
-  </si>
-  <si>
-    <t>1. The menu is deleted.</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>KO</t>
-  </si>
-  <si>
-    <t>1. The menu is not created.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. </t>
-  </si>
-  <si>
-    <t>Falta la tilde.
-https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
-NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-  </si>
-  <si>
-    <t>PTE</t>
-  </si>
-  <si>
-    <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-  </si>
-  <si>
-    <t>MEN006</t>
-  </si>
-  <si>
-    <t>Fields not mandatory with an error</t>
-  </si>
-  <si>
-    <t>1. An error is not shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user fills the fields.
-3. The user clicks  "Crear menú"
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
-2. The user modify a field.
-3. The user clicks  "Modificar menú"
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user selects the menu
-3. The user clicks  "Borrar menu"
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user does not the mandatories fields
-3. The user clicks  "Guardar menu"
-</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -220,27 +88,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -249,7 +120,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
+          <bgColor theme="3" tint="0.5999633777886288"/>
         </patternFill>
       </fill>
     </dxf>
@@ -320,19 +191,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF6565"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -620,202 +479,307 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" customWidth="1"/>
-    <col min="5" max="6" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="41.5703125" customWidth="1" min="4" max="4"/>
+    <col width="33.42578125" customWidth="1" min="5" max="6"/>
+    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="1" s="7">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pasos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Obtained Result</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="75" customFormat="1" customHeight="1" s="6">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>MEN001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Menus' home</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user sees the menus' home
+</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>1. The menus' home is correctly.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>1. The menus' home is not correctly.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Falta la tilde.
+https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
+NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customFormat="1" customHeight="1" s="6">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>MEN002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Create menu</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user fills the fields.
+3. The user clicks  "Crear menú"
+</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1. The menu is created.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>El menú creado aparece listado en la sección Menús</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>SOLUCIONADO: Backend owner.service.ts - la creación de product + menuDefinition se envolvió en una $transaction de Prisma para garantizar atomicidad. Si menuDefinition.create falla, el product también se revierte. Además MenusPage.tsx ahora muestra el error en el modal en lugar de un alert().</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="75" customFormat="1" customHeight="1" s="6">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>MEN003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Modify menu</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
+2. The user modify a field.
+3. The user clicks  "Modificar menú"
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. The menu is modified.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="60" customFormat="1" customHeight="1" s="6">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>MEN004</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Delete menu</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user selects the menu
+3. The user clicks  "Borrar menu"
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>1. The menu is deleted.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="60" customFormat="1" customHeight="1" s="7">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>MEN005</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Required fields are missing</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user does not the mandatories fields
+3. The user clicks  "Guardar menu"
+</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>1. An error is shown</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>1. An error is not shown</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customFormat="1" customHeight="1" s="7">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>MEN006</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Fields not mandatory with an error</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user does not the mandatories fields
+3. The user clicks  "Guardar menu"
+</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>1. An error is shown</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>PTE</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="KO">
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="OK">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="2" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="BL">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PTE">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -1,64 +1,196 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134A6EE6-5719-4838-9DDD-BDEA4E42ED29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Pasos</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Obtained Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Menus' home</t>
+  </si>
+  <si>
+    <t>MEN001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the menus' home
+</t>
+  </si>
+  <si>
+    <t>1. The menus' home is correctly.</t>
+  </si>
+  <si>
+    <t>1. The menus' home is not correctly.</t>
+  </si>
+  <si>
+    <t>MEN002</t>
+  </si>
+  <si>
+    <t>Create menu</t>
+  </si>
+  <si>
+    <t>Modify menu</t>
+  </si>
+  <si>
+    <t>Delete menu</t>
+  </si>
+  <si>
+    <t>MEN003</t>
+  </si>
+  <si>
+    <t>MEN004</t>
+  </si>
+  <si>
+    <t>MEN005</t>
+  </si>
+  <si>
+    <t>Required fields are missing</t>
+  </si>
+  <si>
+    <t>1. An error is shown</t>
+  </si>
+  <si>
+    <t>1. The menu is created.</t>
+  </si>
+  <si>
+    <t>1. The menu is modified.</t>
+  </si>
+  <si>
+    <t>1. The menu is deleted.</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>1. The menu is not created.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. </t>
+  </si>
+  <si>
+    <t>Falta la tilde.
+https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
+NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
+  </si>
+  <si>
+    <t>PTE</t>
+  </si>
+  <si>
+    <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
+  </si>
+  <si>
+    <t>MEN006</t>
+  </si>
+  <si>
+    <t>Fields not mandatory with an error</t>
+  </si>
+  <si>
+    <t>1. An error is not shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user fills the fields.
+3. The user clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
+2. The user modify a field.
+3. The user clicks  "Modificar menú"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user selects the menu
+3. The user clicks  "Borrar menu"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user does not the mandatories fields
+3. The user clicks  "Guardar menu"
+</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00276221"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -88,30 +220,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -120,7 +249,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.5999633777886288"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -191,7 +320,19 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6565"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -479,307 +620,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="41.5703125" customWidth="1" min="4" max="4"/>
-    <col width="33.42578125" customWidth="1" min="5" max="6"/>
-    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="6" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="7">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pasos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Obtained Result</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="75" customFormat="1" customHeight="1" s="6">
-      <c r="A2" s="6" t="n">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>MEN001</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Menus' home</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user sees the menus' home
-</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>1. The menus' home is correctly.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1. The menus' home is not correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Falta la tilde.
-https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
-NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-        </is>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" ht="60" customFormat="1" customHeight="1" s="6">
-      <c r="A3" s="6" t="n">
+    <row r="3" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>MEN002</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Create menu</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user fills the fields.
-3. The user clicks  "Crear menú"
-</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1. The menu is created.</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>El menú creado aparece listado en la sección Menús</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>SOLUCIONADO: Backend owner.service.ts - la creación de product + menuDefinition se envolvió en una $transaction de Prisma para garantizar atomicidad. Si menuDefinition.create falla, el product también se revierte. Además MenusPage.tsx ahora muestra el error en el modal en lugar de un alert().</t>
-        </is>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" ht="75" customFormat="1" customHeight="1" s="6">
-      <c r="A4" s="6" t="n">
+    <row r="4" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>MEN003</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Modify menu</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
-2. The user modify a field.
-3. The user clicks  "Modificar menú"
-</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1. The menu is modified.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3"/>
     </row>
-    <row r="5" ht="60" customFormat="1" customHeight="1" s="6">
-      <c r="A5" s="6" t="n">
+    <row r="5" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>MEN004</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Delete menu</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user selects the menu
-3. The user clicks  "Borrar menu"
-</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1. The menu is deleted.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3"/>
     </row>
-    <row r="6" ht="60" customFormat="1" customHeight="1" s="7">
-      <c r="A6" s="6" t="n">
+    <row r="6" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>MEN005</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Required fields are missing</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user does not the mandatories fields
-3. The user clicks  "Guardar menu"
-</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>1. An error is not shown</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-        </is>
+      <c r="B6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="7" ht="60" customFormat="1" customHeight="1" s="7">
-      <c r="A7" s="6" t="n">
+    <row r="7" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>MEN006</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Fields not mandatory with an error</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user does not the mandatories fields
-3. The user clicks  "Guardar menu"
-</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>PTE</t>
-        </is>
+      <c r="B7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="KO">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="2" text="OK">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="BL">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="PTE">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134A6EE6-5719-4838-9DDD-BDEA4E42ED29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71ED9276-5C14-4223-82C0-9AD9BC6B3245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="0" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
   <si>
     <t>Num</t>
   </si>
@@ -65,9 +65,6 @@
     <t>MEN002</t>
   </si>
   <si>
-    <t>Create menu</t>
-  </si>
-  <si>
     <t>Modify menu</t>
   </si>
   <si>
@@ -80,15 +77,6 @@
     <t>MEN004</t>
   </si>
   <si>
-    <t>MEN005</t>
-  </si>
-  <si>
-    <t>Required fields are missing</t>
-  </si>
-  <si>
-    <t>1. An error is shown</t>
-  </si>
-  <si>
     <t>1. The menu is created.</t>
   </si>
   <si>
@@ -98,42 +86,15 @@
     <t>1. The menu is deleted.</t>
   </si>
   <si>
-    <t>BL</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
     <t>1. The menu is not created.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. </t>
   </si>
   <si>
     <t>Falta la tilde.
 https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
 NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-  </si>
-  <si>
-    <t>PTE</t>
-  </si>
-  <si>
-    <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
-  </si>
-  <si>
-    <t>MEN006</t>
-  </si>
-  <si>
-    <t>Fields not mandatory with an error</t>
-  </si>
-  <si>
-    <t>1. An error is not shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user fills the fields.
-3. The user clicks  "Crear menú"
-</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
@@ -148,10 +109,71 @@
 </t>
   </si>
   <si>
+    <t>Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. 
+15/04/26: SOLUCIONADO: Backend owner.service.ts - la creación de product + menuDefinition se envolvió en una $transaction de Prisma para garantizar atomicidad. Si menuDefinition.create falla, el product también se revierte. Además MenusPage.tsx ahora muestra el error en el modal en lugar de un alert().</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Create first menu: mandatory parameters</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user does not the mandatories fields
-3. The user clicks  "Guardar menu"
+2. The user fills  mandatory fields.
+3. The user clicks  "Crear menú"
 </t>
+  </si>
+  <si>
+    <t>Create first menu: all parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user fills all fields.
+3. The user clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t>Create new menu: mandatory parameters.</t>
+  </si>
+  <si>
+    <t>Create new menu:all parameters.</t>
+  </si>
+  <si>
+    <t>Create first menu: cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user fills all fields.
+3. The user clicks  "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>The operation is cancelled.</t>
+  </si>
+  <si>
+    <t>Create new menu: cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear nuevo Menú"
+2. The user fills the fields.
+3. The user clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear nuevo Menú"
+2. The user fills the fields.
+3. The user clicks  "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>16/04/26: Se ha introducido un IVA con 4 digitos, y aparece "INTERNAL SERVER ERROR":menu002.jpg</t>
+  </si>
+  <si>
+    <t>16/04/26: Se ha modificado un IVA con 4 digitos, y aparece "INTERNAL SERVER ERROR":menu002.jpg</t>
+  </si>
+  <si>
+    <t>1. The menu is not modified.</t>
   </si>
 </sst>
 </file>
@@ -220,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -237,29 +259,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -285,36 +290,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -621,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -631,7 +609,7 @@
     <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -677,13 +655,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="4" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -691,132 +669,212 @@
         <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3"/>
       <c r="G4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="G5" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>5</v>
+    <row r="6" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>6</v>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="H7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="KO">
+  <conditionalFormatting sqref="G2:G10">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71ED9276-5C14-4223-82C0-9AD9BC6B3245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="0" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71ED9276-5C14-4223-82C0-9AD9BC6B3245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC077B1-9E1E-420F-AF28-927FC0EC8E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
   <si>
     <t>Num</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Menus' home</t>
   </si>
   <si>
     <t>MEN001</t>
@@ -63,12 +60,6 @@
   </si>
   <si>
     <t>MEN002</t>
-  </si>
-  <si>
-    <t>Modify menu</t>
-  </si>
-  <si>
-    <t>Delete menu</t>
   </si>
   <si>
     <t>MEN003</t>
@@ -97,26 +88,11 @@
 NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú", and select the menu
-2. The user modify a field.
-3. The user clicks  "Modificar menú"
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
-2. The user selects the menu
-3. The user clicks  "Borrar menu"
-</t>
-  </si>
-  <si>
     <t>Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. 
 15/04/26: SOLUCIONADO: Backend owner.service.ts - la creación de product + menuDefinition se envolvió en una $transaction de Prisma para garantizar atomicidad. Si menuDefinition.create falla, el product también se revierte. Además MenusPage.tsx ahora muestra el error en el modal en lugar de un alert().</t>
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>Create first menu: mandatory parameters</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
@@ -125,24 +101,12 @@
 </t>
   </si>
   <si>
-    <t>Create first menu: all parameters</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
 2. The user fills all fields.
 3. The user clicks  "Crear menú"
 </t>
   </si>
   <si>
-    <t>Create new menu: mandatory parameters.</t>
-  </si>
-  <si>
-    <t>Create new menu:all parameters.</t>
-  </si>
-  <si>
-    <t>Create first menu: cancel</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
 2. The user fills all fields.
 3. The user clicks  "Cancelar"
@@ -152,9 +116,6 @@
     <t>The operation is cancelled.</t>
   </si>
   <si>
-    <t>Create new menu: cancel</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. The user clicks"+ Crear nuevo Menú"
 2. The user fills the fields.
 3. The user clicks  "Crear menú"
@@ -174,6 +135,84 @@
   </si>
   <si>
     <t>1. The menu is not modified.</t>
+  </si>
+  <si>
+    <t>Menus: home</t>
+  </si>
+  <si>
+    <t>Menus: Create first menu, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Menus: Create first menu, all parameters</t>
+  </si>
+  <si>
+    <t>Menus: Create first menu, cancel</t>
+  </si>
+  <si>
+    <t>Menus: Create new menu, mandatory parameters.</t>
+  </si>
+  <si>
+    <t>Menus: Create new menu, all parameters.</t>
+  </si>
+  <si>
+    <t>Menus: Create new menu, cancel</t>
+  </si>
+  <si>
+    <t>Menus: Modify</t>
+  </si>
+  <si>
+    <t>Menus: Delete</t>
+  </si>
+  <si>
+    <t>Menus: Delete, cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2. Clicks the garbage icon of a menu
+3. Clicks "Confirmar!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2. Clicks the garbage icon of a menu
+3. Clicks  "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>Menus: Modify, cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2. The user modify fields
+3. The user clicks  "Cancelar"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2. The user modify fields
+3. The user clicks  "Guardar cambios"
+</t>
+  </si>
+  <si>
+    <t>MEN005</t>
+  </si>
+  <si>
+    <t>MEN006</t>
+  </si>
+  <si>
+    <t>MEN007</t>
+  </si>
+  <si>
+    <t>MEN008</t>
+  </si>
+  <si>
+    <t>MEN009</t>
+  </si>
+  <si>
+    <t>MEN010</t>
+  </si>
+  <si>
+    <t>MEN011</t>
   </si>
 </sst>
 </file>
@@ -599,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -640,25 +679,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="4" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -666,204 +705,252 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" s="4" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G2:G12">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/Web/TestCasesWeb/Menus.xlsx
+++ b/Web/TestCasesWeb/Menus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC077B1-9E1E-420F-AF28-927FC0EC8E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094132EA-7F86-4600-96B8-8A3710FF912F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
   <si>
     <t>Num</t>
   </si>
@@ -56,9 +56,6 @@
     <t>1. The menus' home is correctly.</t>
   </si>
   <si>
-    <t>1. The menus' home is not correctly.</t>
-  </si>
-  <si>
     <t>MEN002</t>
   </si>
   <si>
@@ -78,14 +75,6 @@
   </si>
   <si>
     <t>KO</t>
-  </si>
-  <si>
-    <t>1. The menu is not created.</t>
-  </si>
-  <si>
-    <t>Falta la tilde.
-https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
-NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
   </si>
   <si>
     <t>Se crea el menú, xq lo veo en la sección de Productos, pero en "menus" no se lista, ni parece que haya ninguno. 
@@ -128,13 +117,7 @@
 </t>
   </si>
   <si>
-    <t>16/04/26: Se ha introducido un IVA con 4 digitos, y aparece "INTERNAL SERVER ERROR":menu002.jpg</t>
-  </si>
-  <si>
     <t>16/04/26: Se ha modificado un IVA con 4 digitos, y aparece "INTERNAL SERVER ERROR":menu002.jpg</t>
-  </si>
-  <si>
-    <t>1. The menu is not modified.</t>
   </si>
   <si>
     <t>Menus: home</t>
@@ -213,13 +196,66 @@
   </si>
   <si>
     <t>MEN011</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Falta la tilde.
+https://drive.google.com/file/d/1eJt6l1D_V6LJmak01KkOlF4mEOJ6GUXs/view?usp=drive_link
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOTA: comportamiento diferente a otras pantallas, aquí el botón "Continuar" no se activa, si no está relleno el campo obligatorio "Nombre". HAY QUE UNIFICAR EL COMPORTAMIENTO DE LAS PANTALLAS.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear nuevo Menú"
+2. The user fills all fields.
+3. The user clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t>Menus: Create menu with an incorrect tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"+ Crear Primer Menú"
+2. The user fills TAX with an incorrect tax
+3. The user clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2. The user modify TAX with an incorrect tax
+3. The user clicks  "Guardar cambios"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks"Crear Menú"
+2. Fills with an incorrect value  in section
+3. Clicks  "Crear menú"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu.
+2.  Modify with an incorrect  value in section
+3. The user clicks  "Guardar cambios"
+</t>
+  </si>
+  <si>
+    <t>19/05/26: Aparece "INTERNAL SERVER ERROR": MEN003.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +277,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -281,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -299,6 +342,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,13 +684,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
     <col min="4" max="4" width="41.5703125" customWidth="1"/>
-    <col min="5" max="6" width="33.42578125" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
     <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -682,7 +729,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -690,14 +737,12 @@
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="4" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -705,25 +750,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -731,48 +776,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3"/>
     </row>
@@ -781,72 +824,70 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -855,48 +896,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -905,22 +944,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H11" s="3"/>
     </row>
@@ -929,28 +968,124 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="3"/>
+    </row>
+    <row r="15" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G12">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
